--- a/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Head lamp" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grill fitment-High" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grill fitment-Low" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Side seal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Head lamp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Grill fitment-High" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Grill fitment-Low" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Side seal" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -2605,7 +2605,11 @@
       </c>
       <c r="AW18" s="223" t="inlineStr">
         <is>
-          <t>Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet. Cause/Mode mismatch: This Cause (wrong part/mix-up) does not produce a scratch/damage; it aligns with a wrong-variant selection/installation failure mode instead. Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: FITMENT IS NOT FIRM
+          <t>- Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.
+- Cause/Mode mismatch: This Cause (wrong part/mix-up) does not produce a scratch/damage; it aligns with a wrong-variant selection/installation failure mode instead.
+- Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing.
+- AI severity (8) differs from plant-recorded (5) - review recommended.
+- Same Failure Cause text is also used, verbatim, on a different Failure Mode: FITMENT IS NOT FIRM
  WRONG SELECTION OF HEAD LAMP
 ( NOT AS PER MODEL). Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
@@ -2754,7 +2758,10 @@
       </c>
       <c r="AW20" s="223" t="inlineStr">
         <is>
-          <t>Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet. Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing. AI severity (8) differs from plant-recorded (5) - review recommended. Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
+          <t>- Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.
+- Ambiguous - plausible severities: S8 (Headlamp does not turn ON); S7 (Insufficient brightness / dim light). Suggested value is the worst case; review before finalizing.
+- AI severity (8) differs from plant-recorded (5) - review recommended.
+- Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2909,7 @@
       <c r="AV22" s="223" t="inlineStr"/>
       <c r="AW22" s="223" t="inlineStr">
         <is>
-          <t>AI severity (10) differs from plant-recorded (5) - review recommended.</t>
+          <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3066,7 @@
       <c r="AV24" s="223" t="inlineStr"/>
       <c r="AW24" s="223" t="inlineStr">
         <is>
-          <t>AI severity (10) differs from plant-recorded (5) - review recommended.</t>
+          <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3235,7 @@
       </c>
       <c r="AW26" s="223" t="inlineStr">
         <is>
-          <t>Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.</t>
+          <t>- Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3395,7 @@
       <c r="AV28" s="223" t="inlineStr"/>
       <c r="AW28" s="223" t="inlineStr">
         <is>
-          <t>Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
+          <t>- Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3485,8 @@
       </c>
       <c r="AW29" s="223" t="inlineStr">
         <is>
-          <t>Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet. Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
+          <t>- Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.
+- Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
     </row>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
@@ -2438,7 +2438,7 @@
       <c r="AV17" s="208" t="n"/>
       <c r="AW17" s="208" t="n"/>
     </row>
-    <row r="18" ht="102" customFormat="1" customHeight="1" s="8">
+    <row r="18" ht="150" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
         <is>
           <t>HEAD LAMP STAGE</t>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="118.5" customFormat="1" customHeight="1" s="13">
+    <row r="29" ht="180" customFormat="1" customHeight="1" s="13">
       <c r="B29" s="210" t="n"/>
       <c r="C29" s="211" t="n"/>
       <c r="D29" s="210" t="n"/>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
@@ -1611,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.85546875" customWidth="1" min="1" max="1"/>
@@ -1627,6 +1627,8 @@
     <col width="45" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="45" customWidth="1" min="50" max="50"/>
+    <col width="35" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="1">
@@ -2072,6 +2074,8 @@
       <c r="AU13" s="205" t="n"/>
       <c r="AV13" s="205" t="n"/>
       <c r="AW13" s="205" t="n"/>
+      <c r="AX13" s="205" t="n"/>
+      <c r="AY13" s="205" t="n"/>
     </row>
     <row r="14" ht="22.5" customFormat="1" customHeight="1" s="1">
       <c r="A14" s="198" t="n"/>
@@ -2123,6 +2127,8 @@
       <c r="AU14" s="205" t="n"/>
       <c r="AV14" s="205" t="n"/>
       <c r="AW14" s="205" t="n"/>
+      <c r="AX14" s="205" t="n"/>
+      <c r="AY14" s="205" t="n"/>
     </row>
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
@@ -2333,6 +2339,16 @@
       <c r="AW15" s="208" t="inlineStr">
         <is>
           <t>Remark</t>
+        </is>
+      </c>
+      <c r="AX15" s="208" t="inlineStr">
+        <is>
+          <t>AI Review</t>
+        </is>
+      </c>
+      <c r="AY15" s="208" t="inlineStr">
+        <is>
+          <t>Manual Review</t>
         </is>
       </c>
     </row>
@@ -2386,6 +2402,8 @@
       <c r="AU16" s="208" t="n"/>
       <c r="AV16" s="208" t="n"/>
       <c r="AW16" s="208" t="n"/>
+      <c r="AX16" s="208" t="n"/>
+      <c r="AY16" s="208" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
@@ -2437,6 +2455,8 @@
       <c r="AU17" s="208" t="n"/>
       <c r="AV17" s="208" t="n"/>
       <c r="AW17" s="208" t="n"/>
+      <c r="AX17" s="208" t="n"/>
+      <c r="AY17" s="208" t="n"/>
     </row>
     <row r="18" ht="150" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -2614,6 +2634,8 @@
 ( NOT AS PER MODEL). Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AX18" s="223" t="inlineStr"/>
+      <c r="AY18" s="223" t="inlineStr"/>
     </row>
     <row r="19" ht="207" customFormat="1" customHeight="1" s="8">
       <c r="B19" s="210" t="n"/>
@@ -2669,6 +2691,8 @@
       <c r="AU19" s="223" t="n"/>
       <c r="AV19" s="223" t="n"/>
       <c r="AW19" s="223" t="n"/>
+      <c r="AX19" s="223" t="n"/>
+      <c r="AY19" s="223" t="n"/>
     </row>
     <row r="20" ht="117" customFormat="1" customHeight="1" s="8">
       <c r="B20" s="210" t="n"/>
@@ -2764,6 +2788,8 @@
 - Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AX20" s="223" t="inlineStr"/>
+      <c r="AY20" s="223" t="inlineStr"/>
     </row>
     <row r="21" ht="153" customFormat="1" customHeight="1" s="8">
       <c r="B21" s="210" t="n"/>
@@ -2819,6 +2845,8 @@
       <c r="AU21" s="223" t="n"/>
       <c r="AV21" s="223" t="n"/>
       <c r="AW21" s="223" t="n"/>
+      <c r="AX21" s="223" t="n"/>
+      <c r="AY21" s="223" t="n"/>
     </row>
     <row r="22" ht="119.25" customFormat="1" customHeight="1" s="8">
       <c r="B22" s="210" t="n"/>
@@ -2912,6 +2940,8 @@
           <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
+      <c r="AX22" s="223" t="inlineStr"/>
+      <c r="AY22" s="223" t="inlineStr"/>
     </row>
     <row r="23" ht="186.95" customFormat="1" customHeight="1" s="14">
       <c r="B23" s="210" t="n"/>
@@ -2987,6 +3017,8 @@
       <c r="AU23" s="223" t="n"/>
       <c r="AV23" s="223" t="n"/>
       <c r="AW23" s="223" t="n"/>
+      <c r="AX23" s="223" t="n"/>
+      <c r="AY23" s="223" t="n"/>
     </row>
     <row r="24" ht="130.5" customFormat="1" customHeight="1" s="14">
       <c r="B24" s="210" t="n"/>
@@ -3069,6 +3101,8 @@
           <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
+      <c r="AX24" s="223" t="inlineStr"/>
+      <c r="AY24" s="223" t="inlineStr"/>
     </row>
     <row r="25" ht="130.5" customFormat="1" customHeight="1" s="14">
       <c r="B25" s="210" t="n"/>
@@ -3128,6 +3162,8 @@
       <c r="AU25" s="223" t="n"/>
       <c r="AV25" s="223" t="n"/>
       <c r="AW25" s="223" t="n"/>
+      <c r="AX25" s="223" t="n"/>
+      <c r="AY25" s="223" t="n"/>
     </row>
     <row r="26" ht="135" customFormat="1" customHeight="1" s="14">
       <c r="B26" s="210" t="n"/>
@@ -3238,6 +3274,8 @@
           <t>- Merged failure mode (2 distinct modes detected) - see Sub-modes columns for per-mode Severity/Detection/actions. Row-level Severity/Detection above are the worst case; consider splitting this row in the plant sheet.</t>
         </is>
       </c>
+      <c r="AX26" s="223" t="inlineStr"/>
+      <c r="AY26" s="223" t="inlineStr"/>
     </row>
     <row r="27" ht="156" customFormat="1" customHeight="1" s="13">
       <c r="B27" s="210" t="n"/>
@@ -3303,6 +3341,8 @@
       <c r="AU27" s="223" t="n"/>
       <c r="AV27" s="223" t="n"/>
       <c r="AW27" s="223" t="n"/>
+      <c r="AX27" s="223" t="n"/>
+      <c r="AY27" s="223" t="n"/>
     </row>
     <row r="28" ht="151.5" customFormat="1" customHeight="1" s="13">
       <c r="B28" s="210" t="n"/>
@@ -3398,6 +3438,8 @@
           <t>- Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AX28" s="223" t="inlineStr"/>
+      <c r="AY28" s="223" t="inlineStr"/>
     </row>
     <row r="29" ht="180" customFormat="1" customHeight="1" s="13">
       <c r="B29" s="210" t="n"/>
@@ -3489,10 +3531,12 @@
 - Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AX29" s="223" t="inlineStr"/>
+      <c r="AY29" s="223" t="inlineStr"/>
     </row>
     <row r="30" customFormat="1" s="18"/>
   </sheetData>
-  <mergeCells count="187">
+  <mergeCells count="199">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="K18:L29"/>
     <mergeCell ref="I24:J25"/>
@@ -3538,6 +3582,7 @@
     <mergeCell ref="AP15:AP17"/>
     <mergeCell ref="K8:T8"/>
     <mergeCell ref="AR15:AR17"/>
+    <mergeCell ref="AY18:AY19"/>
     <mergeCell ref="Z23:Z25"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="M22:N25"/>
@@ -3550,16 +3595,19 @@
     <mergeCell ref="K7:T7"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="AX15:AX17"/>
     <mergeCell ref="AN20:AN21"/>
     <mergeCell ref="AQ22:AQ23"/>
     <mergeCell ref="AN26:AN27"/>
     <mergeCell ref="AW24:AW25"/>
+    <mergeCell ref="AY24:AY25"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="Z18:Z21"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="AN22:AN23"/>
+    <mergeCell ref="AY15:AY17"/>
     <mergeCell ref="P18:Q19"/>
     <mergeCell ref="AQ15:AQ17"/>
     <mergeCell ref="Y23:Y25"/>
@@ -3579,9 +3627,11 @@
     <mergeCell ref="AA15:AA17"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="AC15:AC17"/>
+    <mergeCell ref="AX20:AX21"/>
     <mergeCell ref="R28:S29"/>
     <mergeCell ref="I26:J27"/>
     <mergeCell ref="AV20:AV21"/>
+    <mergeCell ref="AX22:AX23"/>
     <mergeCell ref="AQ24:AQ25"/>
     <mergeCell ref="AS24:AS25"/>
     <mergeCell ref="AD15:AD17"/>
@@ -3607,6 +3657,7 @@
     <mergeCell ref="O18:O21"/>
     <mergeCell ref="M18:N21"/>
     <mergeCell ref="AO18:AO19"/>
+    <mergeCell ref="AY22:AY23"/>
     <mergeCell ref="AN18:AN19"/>
     <mergeCell ref="A1:R2"/>
     <mergeCell ref="AL15:AL17"/>
@@ -3617,10 +3668,11 @@
     <mergeCell ref="W28:X29"/>
     <mergeCell ref="P20:Q21"/>
     <mergeCell ref="AV24:AV25"/>
+    <mergeCell ref="AX24:AX25"/>
+    <mergeCell ref="AX18:AX19"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="AO22:AO23"/>
     <mergeCell ref="P22:Q23"/>
-    <mergeCell ref="AM13:AW14"/>
     <mergeCell ref="AR22:AR23"/>
     <mergeCell ref="V18:V21"/>
     <mergeCell ref="AT22:AT23"/>
@@ -3636,11 +3688,13 @@
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="I15:J17"/>
     <mergeCell ref="C18:D29"/>
+    <mergeCell ref="AY26:AY27"/>
     <mergeCell ref="A15:B17"/>
     <mergeCell ref="K15:L17"/>
     <mergeCell ref="E18:F29"/>
     <mergeCell ref="W23:X27"/>
     <mergeCell ref="T20:U20"/>
+    <mergeCell ref="AM13:AY14"/>
     <mergeCell ref="I18:J21"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="Y27:Y29"/>
@@ -3662,6 +3716,7 @@
     <mergeCell ref="AW20:AW21"/>
     <mergeCell ref="AO20:AO21"/>
     <mergeCell ref="R21:S21"/>
+    <mergeCell ref="AY20:AY21"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="R15:S17"/>
@@ -3680,6 +3735,7 @@
     <mergeCell ref="AR26:AR27"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="T18:U18"/>
+    <mergeCell ref="AX26:AX27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__with_suggestions_gpt4omini.xlsx
@@ -2133,9 +2133,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -2154,8 +2176,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -2467,36 +2511,293 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 RH / LH HEAD LAMP FITMENT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Connections, Bolt fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 Headlamp assembly in specific design (bulb/LED assembly, lens fitting, aiming, electrical connection)
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Provide adequate illumination of the road ahead during low-light or night conditions
 2. Ensure visibility of the vehicle to other road users
 3. Meet legal/regulatory lighting requirements (beam pattern, intensity, color)</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -2508,32 +2809,185 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. COLLECT THE HEAD LAMP LH / RH SIDE FROM STORAGE AREA AND SCAN THE PART
 2. CONNECT THE 2 CONNECTORS WITH HEAD LAMP
 3. ALIGN THE HEAD LAMP WITH THE BIW AND THEN TIGHT WITH BOLTS
-2. Machine:
-Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Head lamp from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Head lamp from sequencing trolley and scan
 2. Align H/L with BIW, then do the connections with wiring harness with head lamp and tight with bolts
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong Head lamp variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Lens cracked or broken
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Headlamp does not turn ON
 2. Insufficient brightness / dim light
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -2866,16 +3320,82 @@
       <c r="L22" s="210" t="n"/>
       <c r="M22" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wiring harness partially connected (loose fitment)
 2. Electrical connector loose or damaged
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Incorrect beam alignment
 2. Headlamp does not turn ON
 3. Reduced road visibility
 4. Increased risk of accident</t>
+          </r>
         </is>
       </c>
       <c r="N22" s="207" t="n"/>
@@ -3183,16 +3703,103 @@
       <c r="L26" s="210" t="n"/>
       <c r="M26" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting screws under-torqued or over-torqued
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Lens cracked or broken
 2. LED / BULB burnout
 3. Water ingress inside lamp
 4. Rattling or vibration noise during driving
 5. Driver discomfort or eye strain</t>
+          </r>
         </is>
       </c>
       <c r="N26" s="207" t="n"/>
@@ -4228,9 +4835,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -4249,8 +4878,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -4471,37 +5122,294 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 FRONT GRILL FITMENT- HIGH VARIANT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Connections, 
 Bolts &amp; pushpin   fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 To correctly install front grill fitment as per BIW design specifications.
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Allow airflow to the radiator, condenser, and engine compartment
 2. Protect cooling components from debris, stones, insects
 3. Provide vehicle styling and brand identity</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -4513,33 +5421,186 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
 2. CONNECT THE CONNECTORS WITH GRILL
 3. INSERT &amp; 
 ALIGN THE FRONT GRILL WITH BIW AND THEN TIGHT WITH BOLTS AND PUSHPINS
-2. Machine:
-Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Front grill from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Front grill from sequencing trolley and scan
 2. Then do the connections with wiring harness with grill and align with BIW and tight with bolts &amp; pushpins
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong front grill variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Gaps or scratches on grill 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Incorrect distance / object detection
 2. Water/dust ingress affecting sensor
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -4737,16 +5798,82 @@
       <c r="L22" s="210" t="n"/>
       <c r="M22" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wiring harness partially connected (loose fitment)
 2. Wiring harness pinched or damaged
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. False ADAS warnings or alerts
 2. Incorrect object detection
 3. Lane assist / collision warning inoperative
 4. Increased risk of accident</t>
+          </r>
         </is>
       </c>
       <c r="N22" s="207" t="n"/>
@@ -4953,16 +6080,103 @@
       <c r="L26" s="210" t="n"/>
       <c r="M26" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting bolts under-torqued or over-torqued
 3. Broken clips
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Customer loss of confidence in vehicle safety
 2. False collision warnings provided to driver
 3. Water/dust ingress affecting sensor
 4. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N26" s="207" t="n"/>
@@ -5764,9 +6978,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -5785,8 +7021,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -6007,36 +7265,293 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 FRONT GRILL FITMENT- LOW VARIANT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Bolts &amp; pushpin   fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 To correctly install front grill fitment as per BIW design specifications.
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Allow airflow to the radiator, condenser, and engine compartment
 2. Protect cooling components from debris, stones, insects
 3. Provide vehicle styling and brand identity</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -6048,32 +7563,185 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
 2. INSERT &amp; 
 ALIGN THE FRONT GRILL WITH BIW AND THEN TIGHT WITH BOLTS AND PUSHPINS
-2. Machine:
-Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Front grill from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Front grill from sequencing trolley and scan
 2. Align with BIW and tight with bolts &amp; pushpins
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong front grill variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Gaps or scratches on grill 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting sensor
 2. Customer dissatisfaction
 3. Bad appereance of vehicle</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -6234,11 +7902,77 @@
       <c r="L21" s="210" t="n"/>
       <c r="M21" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting part warrenty</t>
+          </r>
         </is>
       </c>
       <c r="N21" s="207" t="n"/>
@@ -6414,14 +8148,101 @@
       <c r="L24" s="210" t="n"/>
       <c r="M24" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting bolts under-torqued or over-torqued
 3. Broken clips
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting sensor
 2. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N24" s="207" t="n"/>
@@ -7235,9 +9056,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -7256,8 +9099,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -7478,37 +9343,294 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 LH / RH RADIATOR SIDE SEAL FITMENT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Screw &amp; pushpin fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Correct installation and positioning of the side seal during radiator assembly.
 2. Maintain seal integrity (no cuts, twists or misalignment)
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Maintain system pressure under operating temperature and vibration
 2. Accommodate thermal expansion between radiator components
 3. Seal the joint between the radiator core and side tank to prevent coolant leakage</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -7520,30 +9642,183 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. GET THE SIDE SEAL FROM STORAGE BIN
 2. ALIGN THE SIDE SEAL WITH THE BIW AND THEN TIGHT WITH BOLT AND PUSHPIN
-2. Machine:
-Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Take side seal from storage bin
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Take side seal from storage bin
 2. Align side seal with BIW and tight with bolt and pushpin
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong part installed or mixed material
 2. FURTHER OPERATION NOT POSSIBLE
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Vehicle overheating
 2. Coolant seepage or visible leak
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -7652,15 +9927,81 @@
       <c r="L20" s="210" t="n"/>
       <c r="M20" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Cut, torn, pinched, or cracked seal
 2. Seal under-compressed or over-compressed
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Reduced cooling efficiency
 2. Engine overheating
 3. Safety risk if overheating occurs during driving</t>
+          </r>
         </is>
       </c>
       <c r="N20" s="207" t="n"/>
@@ -7929,14 +10270,101 @@
       <c r="L25" s="210" t="n"/>
       <c r="M25" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting Bolt under-torqued or over-torqued
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Customer dissatisfaction due to coolant leak
 2. Coolant dripping under vehicle
 3. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N25" s="207" t="n"/>
